--- a/data/trans_dic/P40_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P40_R-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,25%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>87,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>92,83%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>93,91; 97,57</t>
+          <t>94,06; 97,59</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>95,99; 98,86</t>
+          <t>95,93; 98,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>92,58; 96,98</t>
+          <t>92,69; 97,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>92,38; 99,35</t>
+          <t>93,66; 99,26</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,44; 94,23</t>
+          <t>89,99; 94,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,13; 94,47</t>
+          <t>89,73; 94,74</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,76; 97,2</t>
+          <t>93,17; 97,23</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82,87; 93,37</t>
+          <t>82,19; 92,13</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>92,66; 95,59</t>
+          <t>92,67; 95,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>93,5; 96,42</t>
+          <t>93,41; 96,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>93,51; 96,66</t>
+          <t>93,71; 96,88</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>90,41; 96,2</t>
+          <t>89,69; 95,16</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,13%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,01%</t>
+          <t>93,12%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>93,12; 96,41</t>
+          <t>93,23; 96,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>91,34; 95,43</t>
+          <t>91,04; 95,27</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>93,56; 97,12</t>
+          <t>93,45; 97,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>89,21; 95,41</t>
+          <t>89,78; 95,72</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>83,97; 89,51</t>
+          <t>84,08; 89,45</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>88,51; 93,34</t>
+          <t>88,4; 93,22</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>91,34; 95,45</t>
+          <t>91,11; 95,44</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>47,18; 93,63</t>
+          <t>90,37; 95,36</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>89,62; 92,79</t>
+          <t>89,53; 92,85</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>90,51; 93,68</t>
+          <t>90,63; 93,74</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>93,06; 95,82</t>
+          <t>93,1; 95,76</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>64,92; 93,55</t>
+          <t>91,06; 94,83</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>91,28%</t>
+          <t>92,37%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>86,76%</t>
+          <t>86,8%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>89,01%</t>
+          <t>89,58%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>86,25; 91,3</t>
+          <t>86,23; 91,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>87,71; 92,63</t>
+          <t>87,37; 92,51</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>89,74; 94,2</t>
+          <t>89,69; 94,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>88,47; 93,56</t>
+          <t>89,67; 94,26</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>78,06; 83,99</t>
+          <t>77,73; 83,97</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>80,84; 86,38</t>
+          <t>80,63; 86,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>86,99; 91,79</t>
+          <t>87,15; 91,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>84,48; 89,17</t>
+          <t>84,34; 88,89</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>82,79; 86,71</t>
+          <t>82,87; 86,67</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>85,02; 88,58</t>
+          <t>84,98; 88,82</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>89,12; 92,37</t>
+          <t>89,11; 92,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>87,27; 90,65</t>
+          <t>88,0; 91,13</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86,39%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>76,84%</t>
+          <t>76,69%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>82,14%</t>
+          <t>79,29%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>83,36; 89,19</t>
+          <t>83,37; 89,51</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>81,55; 87,86</t>
+          <t>81,46; 87,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81,22; 86,95</t>
+          <t>80,81; 86,92</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,08; 94,25</t>
+          <t>78,96; 84,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>69,21; 76,62</t>
+          <t>69,04; 76,51</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,41; 79,64</t>
+          <t>72,47; 79,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,48; 82,07</t>
+          <t>75,34; 82,1</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>73,91; 80,41</t>
+          <t>74,25; 79,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>77,21; 82,2</t>
+          <t>77,34; 82,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77,78; 82,78</t>
+          <t>77,75; 82,58</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>79,29; 83,79</t>
+          <t>79,09; 83,53</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>78,03; 88,57</t>
+          <t>77,33; 81,26</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>69,6%</t>
+          <t>70,61%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>67,38%</t>
+          <t>67,65%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>66,22; 75,04</t>
+          <t>66,4; 75,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>67,91; 76,61</t>
+          <t>68,11; 77,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72,17; 80,08</t>
+          <t>72,52; 80,06</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>66,0; 73,22</t>
+          <t>66,93; 74,06</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>55,92; 65,51</t>
+          <t>56,23; 65,87</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,01; 66,35</t>
+          <t>57,16; 66,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,13; 66,33</t>
+          <t>57,62; 66,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>61,67; 68,06</t>
+          <t>61,77; 67,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>62,46; 69,0</t>
+          <t>62,7; 69,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>63,68; 70,42</t>
+          <t>64,01; 70,52</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,77; 72,02</t>
+          <t>65,95; 72,13</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>64,95; 69,78</t>
+          <t>65,52; 69,93</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>70,73%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>71,76%</t>
+          <t>57,2%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>63,71%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>58,84; 69,48</t>
+          <t>59,38; 70,34</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>59,97; 71,44</t>
+          <t>59,91; 71,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>63,63; 73,7</t>
+          <t>63,58; 73,87</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>66,49; 73,78</t>
+          <t>67,38; 74,7</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>35,85; 46,07</t>
+          <t>35,62; 46,31</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>44,81; 55,49</t>
+          <t>45,3; 56,17</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>45,25; 55,88</t>
+          <t>45,74; 55,81</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>56,22; 86,63</t>
+          <t>53,59; 60,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>47,63; 55,31</t>
+          <t>47,77; 55,39</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>53,67; 61,42</t>
+          <t>54,2; 61,74</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>55,47; 63,2</t>
+          <t>55,65; 62,92</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>62,55; 84,62</t>
+          <t>61,13; 66,42</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>36,65%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>43,57%</t>
+          <t>43,69%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>38,65; 53,08</t>
+          <t>39,92; 53,32</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>37,95; 51,64</t>
+          <t>38,05; 51,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>46,28; 57,72</t>
+          <t>46,29; 57,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49,28; 58,7</t>
+          <t>48,71; 58,78</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>30,11; 40,79</t>
+          <t>29,82; 41,05</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>28,04; 38,3</t>
+          <t>28,2; 38,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>30,35; 41,46</t>
+          <t>30,28; 41,22</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>33,57; 39,99</t>
+          <t>33,78; 40,49</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>35,28; 43,82</t>
+          <t>35,15; 43,52</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>33,74; 41,69</t>
+          <t>33,8; 41,57</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>38,09; 46,11</t>
+          <t>37,94; 46,34</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>40,66; 46,03</t>
+          <t>41,13; 46,47</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>72,59%</t>
+          <t>72,46%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>76,79%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>82,67; 85,29</t>
+          <t>82,78; 85,25</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>81,61; 84,39</t>
+          <t>81,59; 84,45</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>82,69; 85,25</t>
+          <t>82,6; 85,29</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>80,16; 85,94</t>
+          <t>79,98; 82,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>69,85; 73,07</t>
+          <t>69,81; 72,99</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>71,53; 74,64</t>
+          <t>71,51; 74,53</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>73,22; 76,33</t>
+          <t>73,2; 76,26</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>68,71; 77,11</t>
+          <t>71,19; 73,71</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>76,63; 78,6</t>
+          <t>76,59; 78,7</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>76,96; 78,95</t>
+          <t>76,91; 79,11</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>78,41; 80,23</t>
+          <t>78,26; 80,32</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>74,83; 80,02</t>
+          <t>75,89; 77,65</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con estado de salud bueno o muy bueno (tasa de respuesta: 99,57%)</t>
+          <t>Población cuya salud autopercibida en los últimos 12 meses es buena o muy buena (tasa de respuesta: 99,57%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>389407</t>
+          <t>396561</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>279301</t>
+          <t>318480</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>668708</t>
+          <t>715041</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>463955; 482067</t>
+          <t>464701; 482181</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>423327; 436016</t>
+          <t>423087; 436008</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>385650; 404005</t>
+          <t>386110; 404842</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>369494; 397373</t>
+          <t>381939; 404766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>418127; 440510</t>
+          <t>420673; 442162</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>375307; 397813</t>
+          <t>377854; 398953</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>364848; 382324</t>
+          <t>366474; 382436</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>259546; 292443</t>
+          <t>297939; 333991</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>890959; 919137</t>
+          <t>891071; 919826</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>806084; 831229</t>
+          <t>805308; 831766</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>757340; 782907</t>
+          <t>758964; 784685</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>644757; 686084</t>
+          <t>690892; 733032</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>392946</t>
+          <t>444124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>411275</t>
+          <t>466529</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>804222</t>
+          <t>910652</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>684917; 709102</t>
+          <t>685668; 708603</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>614187; 641729</t>
+          <t>612193; 640603</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>547485; 568330</t>
+          <t>546838; 567687</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>377831; 404086</t>
+          <t>428140; 456496</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>525223; 559874</t>
+          <t>525941; 559474</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>534724; 563915</t>
+          <t>534082; 563168</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>507086; 529905</t>
+          <t>505825; 529831</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>241324; 478938</t>
+          <t>452847; 477837</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1219757; 1262810</t>
+          <t>1218510; 1263703</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>1155388; 1195946</t>
+          <t>1157044; 1196682</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1061202; 1092653</t>
+          <t>1061590; 1091929</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>607056; 874760</t>
+          <t>890534; 927407</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>489576</t>
+          <t>573488</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>470649</t>
+          <t>540014</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>960225</t>
+          <t>1113502</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>550879; 583126</t>
+          <t>550694; 582739</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>590118; 623202</t>
+          <t>587827; 622446</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>599490; 629297</t>
+          <t>599141; 628324</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>474502; 501791</t>
+          <t>556711; 585219</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>538428; 579349</t>
+          <t>536119; 579202</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>569932; 609025</t>
+          <t>568486; 609548</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>568897; 600309</t>
+          <t>569937; 601014</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>458285; 483729</t>
+          <t>524703; 552992</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1099794; 1151896</t>
+          <t>1100890; 1151284</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1171465; 1220498</t>
+          <t>1170936; 1223762</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1178198; 1221174</t>
+          <t>1178056; 1220923</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>941518; 977946</t>
+          <t>1093775; 1132766</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>766960</t>
+          <t>574642</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>547517</t>
+          <t>564837</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1314478</t>
+          <t>1139479</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>431175; 461336</t>
+          <t>431226; 462989</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>497574; 536078</t>
+          <t>497016; 536471</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>522383; 559214</t>
+          <t>519732; 558994</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>710968; 836755</t>
+          <t>553212; 594322</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>356853; 395072</t>
+          <t>356010; 394520</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>445420; 489855</t>
+          <t>445746; 489374</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>486643; 529177</t>
+          <t>485750; 529371</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>526632; 572948</t>
+          <t>546877; 582512</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>797468; 849011</t>
+          <t>798825; 849272</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>953033; 1014322</t>
+          <t>952673; 1011880</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1021143; 1079107</t>
+          <t>1018637; 1075752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>1248671; 1417448</t>
+          <t>1111352; 1167857</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>390597</t>
+          <t>430249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>356776</t>
+          <t>393851</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>747373</t>
+          <t>824101</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>255458; 289482</t>
+          <t>256132; 291166</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>290206; 327379</t>
+          <t>291074; 329788</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>340971; 378313</t>
+          <t>342616; 378233</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>370431; 410958</t>
+          <t>407821; 451289</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>225371; 264060</t>
+          <t>226621; 265496</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>255305; 297110</t>
+          <t>255970; 298873</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>282497; 327979</t>
+          <t>284912; 330295</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>337883; 372918</t>
+          <t>376068; 412230</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>492734; 544251</t>
+          <t>494568; 547783</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>557289; 616266</t>
+          <t>560207; 617176</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>635900; 696359</t>
+          <t>637662; 697473</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>720401; 773927</t>
+          <t>798137; 851863</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>258364</t>
+          <t>287942</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>436549</t>
+          <t>251221</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>694914</t>
+          <t>539162</t>
         </is>
       </c>
     </row>
@@ -3108,62 +3108,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>172163; 203290</t>
+          <t>173727; 205812</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>185779; 221297</t>
+          <t>185591; 222383</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>210995; 244386</t>
+          <t>210831; 244964</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>244808; 271649</t>
+          <t>274284; 304093</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>122628; 157596</t>
+          <t>121851; 158421</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>158622; 196425</t>
+          <t>160374; 198835</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>169089; 208845</t>
+          <t>170921; 208559</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>342052; 527038</t>
+          <t>235328; 265309</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>302296; 351029</t>
+          <t>303189; 351538</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>356248; 407700</t>
+          <t>359738; 409794</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>391234; 445771</t>
+          <t>392529; 443774</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>610869; 826389</t>
+          <t>517339; 562066</t>
         </is>
       </c>
     </row>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>152701</t>
+          <t>167228</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>156065</t>
+          <t>171317</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>308766</t>
+          <t>338546</t>
         </is>
       </c>
     </row>
@@ -3316,62 +3316,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>81119; 111407</t>
+          <t>83775; 111913</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>94448; 128515</t>
+          <t>94689; 128488</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118609; 147918</t>
+          <t>118622; 147912</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>139339; 165979</t>
+          <t>151111; 182325</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>100554; 136188</t>
+          <t>99573; 137063</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>108791; 148569</t>
+          <t>109411; 150279</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>121032; 165364</t>
+          <t>120774; 164406</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>142951; 170300</t>
+          <t>156941; 188143</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>191827; 238279</t>
+          <t>191153; 236654</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>214819; 265440</t>
+          <t>215235; 264710</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>249495; 302038</t>
+          <t>248519; 303585</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>288135; 326155</t>
+          <t>318686; 360042</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>2840552</t>
+          <t>2874234</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>2658133</t>
+          <t>2706250</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5498686</t>
+          <t>5580484</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2706368; 2792019</t>
+          <t>2710132; 2790716</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2760419; 2854379</t>
+          <t>2759784; 2856332</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2789225; 2875766</t>
+          <t>2786301; 2877168</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2773520; 2973323</t>
+          <t>2825560; 2918160</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>2359049; 2467710</t>
+          <t>2357868; 2465095</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>2528669; 2638493</t>
+          <t>2528033; 2634771</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>2573184; 2682369</t>
+          <t>2572527; 2680009</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>2515853; 2823690</t>
+          <t>2658907; 2753058</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>5096678; 5227843</t>
+          <t>5094118; 5234445</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>5323512; 5461653</t>
+          <t>5320468; 5472520</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>5400612; 5525809</t>
+          <t>5390043; 5532141</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>5329362; 5698928</t>
+          <t>5515307; 5643081</t>
         </is>
       </c>
     </row>
